--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-08-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-08-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff740186b25+79621]
-	GetHandleVerifier [0x0x7ff740186b80+79712]
-	(No symbol) [0x0x7ff73ff1c0ea]
-	(No symbol) [0x0x7ff73ff72f56]
-	(No symbol) [0x0x7ff73ff7320c]
-	(No symbol) [0x0x7ff73ffc65b7]
-	(No symbol) [0x0x7ff73ff9b17f]
-	(No symbol) [0x0x7ff73ffc33d0]
-	(No symbol) [0x0x7ff73ff9af13]
-	(No symbol) [0x0x7ff73ff64151]
-	(No symbol) [0x0x7ff73ff64ee3]
-	GetHandleVerifier [0x0x7ff74044683d+2962461]
-	GetHandleVerifier [0x0x7ff740440b5d+2938685]
-	GetHandleVerifier [0x0x7ff74045f71d+3064573]
-	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
-	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
-	GetHandleVerifier [0x0x7ff74018f914+115956]
-	GetHandleVerifier [0x0x7ff74018fac9+116393]
-	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	GetHandleVerifier [0x0x7ff76dfd6b25+79621]
+	GetHandleVerifier [0x0x7ff76dfd6b80+79712]
+	(No symbol) [0x0x7ff76dd6c0ea]
+	(No symbol) [0x0x7ff76ddc2f56]
+	(No symbol) [0x0x7ff76ddc320c]
+	(No symbol) [0x0x7ff76de165b7]
+	(No symbol) [0x0x7ff76ddeb17f]
+	(No symbol) [0x0x7ff76de133d0]
+	(No symbol) [0x0x7ff76ddeaf13]
+	(No symbol) [0x0x7ff76ddb4151]
+	(No symbol) [0x0x7ff76ddb4ee3]
+	GetHandleVerifier [0x0x7ff76e29683d+2962461]
+	GetHandleVerifier [0x0x7ff76e290b5d+2938685]
+	GetHandleVerifier [0x0x7ff76e2af71d+3064573]
+	GetHandleVerifier [0x0x7ff76dff0c6e+186446]
+	GetHandleVerifier [0x0x7ff76dff8a3f+218655]
+	GetHandleVerifier [0x0x7ff76dfdf914+115956]
+	GetHandleVerifier [0x0x7ff76dfdfac9+116393]
+	GetHandleVerifier [0x0x7ff76dfc5ef8+10968]
 	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
 	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
